--- a/Employee_Reports_wi48/Abeykoon Mudiyanselage Sasitha Dinushka Abeykoon Q0629.xlsx
+++ b/Employee_Reports_wi48/Abeykoon Mudiyanselage Sasitha Dinushka Abeykoon Q0629.xlsx
@@ -445,14 +445,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="73" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
@@ -524,6 +524,902 @@
           <t>REMARKS</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Stacker crane (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-002</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>23-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>22-Apr-2028</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>646</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>EWS EQ  (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-004</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>22-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>21-Apr-2028</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>645</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>CS-H9-TV (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-003</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>23-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>22-Apr-2028</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>646</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>ULD&amp;BB-TV (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-010</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>22-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>21-Apr-2028</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>645</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>FMC-deck (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-005</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>26-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>25-Apr-2028</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>649</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Tilting deck (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-009</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>26-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>25-Apr-2028</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>649</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>TT+RA (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-007</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>23-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>22-Apr-2028</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>646</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>CS-Hoist (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-001</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>23-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>22-Apr-2028</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>646</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>ULD Hoist (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-008</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>26-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>25-Apr-2028</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>649</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Truck dock (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-006</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>26-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>25-Apr-2028</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>649</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Cool Room (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-011</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>26-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>25-Apr-2028</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>649</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Climate Control Center (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-014</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>26-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>25-Apr-2028</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>649</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Powered roller Decks2 (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>26-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>25-Apr-2028</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>649</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Lodige LOTO Procedure (SOPs)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>ELECTRICAL SAFETY</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>LSME-OHS-SOP-021</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>26-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>26-Apr-2027</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>284</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Equipment Operation Procedure
+(SOP-031) (SOPs)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-031</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>23-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>23-Apr-2027</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>281</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Stacker Crane Aisle Annual Maintenance And Megger Test Procedure (SOPs)</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-003</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>26-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>26-Apr-2027</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>284</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>POWERED ROLLER DECK(matarSOP) (SOPs)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>26-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>26-Apr-2027</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>284</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>26-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>26-Apr-2027</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>284</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Matar LOTO Procedure (SOPs)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>MATAR</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>FM-DE-24-SOP-SA-013</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>26-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>26-Apr-2027</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>284</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -677,7 +1573,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7945</v>
+        <v>7942</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -772,7 +1668,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7940</v>
+        <v>7937</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -801,7 +1697,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7940</v>
+        <v>7937</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -830,7 +1726,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7937</v>
+        <v>7934</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -859,7 +1755,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7937</v>
+        <v>7934</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -888,7 +1784,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7937</v>
+        <v>7934</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -917,7 +1813,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -946,7 +1842,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -975,7 +1871,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7940</v>
+        <v>7937</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1004,7 +1900,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1033,7 +1929,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1062,7 +1958,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
